--- a/exports/trend_1d/WAAREEENER_full_report.xlsx
+++ b/exports/trend_1d/WAAREEENER_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>17.49</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>45652</v>
+        <v>45653</v>
       </c>
       <c r="H2" t="n">
-        <v>2823.15</v>
+        <v>2790.4</v>
       </c>
       <c r="I2" t="n">
         <v>2809.226739413215</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01</v>
+        <v>-1.15</v>
       </c>
       <c r="L2" t="n">
         <v>11.01</v>
@@ -564,7 +587,19 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>16.97</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>45737</v>
+        <v>45740</v>
       </c>
       <c r="H3" t="n">
-        <v>2352.9</v>
+        <v>2431.35</v>
       </c>
       <c r="I3" t="n">
         <v>2396.024121106525</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K3" t="n">
-        <v>15.68</v>
+        <v>12.87</v>
       </c>
       <c r="L3" t="n">
         <v>4.14</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>12.18</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>45750</v>
+        <v>45751</v>
       </c>
       <c r="H4" t="n">
-        <v>2233.05</v>
+        <v>2160.95</v>
       </c>
       <c r="I4" t="n">
         <v>2162.740318734524</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K4" t="n">
-        <v>-8.16</v>
+        <v>-11.12</v>
       </c>
       <c r="L4" t="n">
-        <v>9.31</v>
+        <v>12.34</v>
       </c>
       <c r="M4" t="n">
         <v>1.77</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>13.45</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>45764</v>
+        <v>45768</v>
       </c>
       <c r="H5" t="n">
-        <v>2323</v>
+        <v>2444.2</v>
       </c>
       <c r="I5" t="n">
         <v>2332.210920499838</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K5" t="n">
-        <v>-7.5</v>
+        <v>-13.11</v>
       </c>
       <c r="L5" t="n">
-        <v>10</v>
+        <v>14.12</v>
       </c>
       <c r="M5" t="n">
         <v>4.22</v>
       </c>
       <c r="N5" t="n">
-        <v>4.19</v>
+        <v>5.22</v>
       </c>
       <c r="O5" t="n">
         <v>-3.23</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>14.56</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>45882</v>
+        <v>45883</v>
       </c>
       <c r="H6" t="n">
-        <v>2941.9</v>
+        <v>2882.8</v>
       </c>
       <c r="I6" t="n">
         <v>2914.154470317832</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K6" t="n">
-        <v>20.36</v>
+        <v>17.94</v>
       </c>
       <c r="L6" t="n">
         <v>4.05</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>13.99</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>45895</v>
+        <v>45897</v>
       </c>
       <c r="H7" t="n">
-        <v>3265.3</v>
+        <v>3417.3</v>
       </c>
       <c r="I7" t="n">
         <v>3286.150675946084</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K7" t="n">
-        <v>-13.27</v>
+        <v>-18.54</v>
       </c>
       <c r="L7" t="n">
-        <v>15.51</v>
+        <v>19.6</v>
       </c>
       <c r="M7" t="n">
         <v>2.3</v>
       </c>
       <c r="N7" t="n">
-        <v>3.75</v>
+        <v>4.66</v>
       </c>
       <c r="O7" t="n">
         <v>-2.01</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>13.67</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="H8" t="n">
-        <v>3445.1</v>
+        <v>3207.6</v>
       </c>
       <c r="I8" t="n">
         <v>3250.650641352855</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8100000000000001</v>
+        <v>-6.14</v>
       </c>
       <c r="L8" t="n">
         <v>7.79</v>
@@ -897,7 +992,7 @@
         <v>3.57</v>
       </c>
       <c r="N8" t="n">
-        <v>5.92</v>
+        <v>6.89</v>
       </c>
       <c r="O8" t="n">
         <v>4.66</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>15.71</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="H9" t="n">
-        <v>2748.5</v>
+        <v>2787.5</v>
       </c>
       <c r="I9" t="n">
         <v>2756.666982587572</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K9" t="n">
-        <v>14.31</v>
+        <v>13.1</v>
       </c>
       <c r="L9" t="n">
         <v>15.94</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>6</v>
+      </c>
+      <c r="U9" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>13.34</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="H10" t="n">
-        <v>3023.5</v>
+        <v>2708.5</v>
       </c>
       <c r="I10" t="n">
         <v>2810.635130482015</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K10" t="n">
-        <v>8.470000000000001</v>
+        <v>-2.83</v>
       </c>
       <c r="L10" t="n">
         <v>8.630000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>1.27</v>
+        <v>6.76</v>
       </c>
       <c r="N10" t="n">
-        <v>5.03</v>
+        <v>10.42</v>
       </c>
       <c r="O10" t="n">
         <v>1.42</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>15.23</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="H11" t="n">
-        <v>2883.1</v>
+        <v>3184.8</v>
       </c>
       <c r="I11" t="n">
         <v>2903.695489529586</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K11" t="n">
-        <v>-6.45</v>
+        <v>-17.59</v>
       </c>
       <c r="L11" t="n">
-        <v>9.470000000000001</v>
+        <v>19.03</v>
       </c>
       <c r="M11" t="n">
         <v>1.72</v>
       </c>
       <c r="N11" t="n">
-        <v>3.31</v>
+        <v>10.46</v>
       </c>
       <c r="O11" t="n">
         <v>-10.42</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>17.12</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="H12" t="n">
-        <v>3502.9</v>
+        <v>3118.8</v>
       </c>
       <c r="I12" t="n">
         <v>3178.07647671838</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K12" t="n">
-        <v>9.99</v>
+        <v>-2.07</v>
       </c>
       <c r="L12" t="n">
         <v>9.26</v>
       </c>
       <c r="M12" t="n">
-        <v>2.82</v>
+        <v>5.79</v>
       </c>
       <c r="N12" t="n">
-        <v>3.2</v>
+        <v>10.97</v>
       </c>
       <c r="O12" t="n">
         <v>10.46</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>16.27</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="H13" t="n">
-        <v>2451</v>
+        <v>2516</v>
       </c>
       <c r="I13" t="n">
         <v>2502.012348896547</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K13" t="n">
-        <v>21.41</v>
+        <v>19.33</v>
       </c>
       <c r="L13" t="n">
         <v>6.61</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>6</v>
+      </c>
+      <c r="U13" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>9.869999999999999</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="H14" t="n">
-        <v>2319</v>
+        <v>2275</v>
       </c>
       <c r="I14" t="n">
         <v>2312.86630649007</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K14" t="n">
-        <v>-7.83</v>
+        <v>-9.58</v>
       </c>
       <c r="L14" t="n">
-        <v>8.779999999999999</v>
+        <v>10.21</v>
       </c>
       <c r="M14" t="n">
         <v>1.96</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1299,6 +1478,12 @@
       <c r="Q15" t="n">
         <v>2</v>
       </c>
+      <c r="R15" s="3" t="n">
+        <v>46350</v>
+      </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2279,7 +2464,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>53.5</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6">
@@ -2289,7 +2474,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7">
@@ -2299,7 +2484,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8">
@@ -2309,7 +2494,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
@@ -2319,7 +2504,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10">
@@ -2329,7 +2514,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>122.8</v>
+        <v>123.8</v>
       </c>
     </row>
     <row r="11">
@@ -2369,7 +2554,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.68</v>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="15">
@@ -2379,7 +2564,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.38</v>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="16">
@@ -2389,7 +2574,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.03</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="17">
@@ -2399,7 +2584,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>21.41</v>
+        <v>19.33</v>
       </c>
     </row>
     <row r="18">
@@ -2409,7 +2594,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>61.5</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="19">
@@ -2419,7 +2604,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>9.27</v>
+        <v>10.98</v>
       </c>
     </row>
     <row r="20">
@@ -2429,7 +2614,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9.26</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="21">
@@ -2439,7 +2624,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15.94</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="22">
@@ -2459,7 +2644,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -2469,7 +2654,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.92</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="25">
@@ -2489,7 +2674,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.64</v>
+        <v>7.43</v>
       </c>
     </row>
     <row r="27">
@@ -2499,7 +2684,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9.92</v>
+        <v>10.97</v>
       </c>
     </row>
     <row r="28">
@@ -2509,7 +2694,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29">
